--- a/Team-Data/2008-09/11-17-2008-09.xlsx
+++ b/Team-Data/2008-09/11-17-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,16 +806,16 @@
         <v>4</v>
       </c>
       <c r="AD2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AE2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF2" t="n">
         <v>4</v>
       </c>
       <c r="AG2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH2" t="n">
         <v>17</v>
@@ -772,7 +839,7 @@
         <v>1</v>
       </c>
       <c r="AO2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP2" t="n">
         <v>15</v>
@@ -790,7 +857,7 @@
         <v>19</v>
       </c>
       <c r="AU2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV2" t="n">
         <v>8</v>
@@ -799,19 +866,19 @@
         <v>13</v>
       </c>
       <c r="AX2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY2" t="n">
         <v>19</v>
       </c>
       <c r="AZ2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA2" t="n">
         <v>17</v>
       </c>
       <c r="BB2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BC2" t="n">
         <v>7</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>11-17-2008-09</t>
+          <t>2008-11-17</t>
         </is>
       </c>
     </row>
@@ -843,16 +910,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="H3" t="n">
         <v>48.5</v>
@@ -861,82 +928,82 @@
         <v>33</v>
       </c>
       <c r="J3" t="n">
-        <v>75.3</v>
+        <v>75.2</v>
       </c>
       <c r="K3" t="n">
-        <v>0.438</v>
+        <v>0.439</v>
       </c>
       <c r="L3" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="M3" t="n">
-        <v>16.9</v>
+        <v>16.6</v>
       </c>
       <c r="N3" t="n">
-        <v>0.314</v>
+        <v>0.306</v>
       </c>
       <c r="O3" t="n">
-        <v>23.4</v>
+        <v>23.2</v>
       </c>
       <c r="P3" t="n">
-        <v>30</v>
+        <v>30.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.78</v>
+        <v>0.763</v>
       </c>
       <c r="R3" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="S3" t="n">
-        <v>32.9</v>
+        <v>32.3</v>
       </c>
       <c r="T3" t="n">
-        <v>44</v>
+        <v>43.3</v>
       </c>
       <c r="U3" t="n">
-        <v>20.5</v>
+        <v>20.1</v>
       </c>
       <c r="V3" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="W3" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X3" t="n">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="Z3" t="n">
-        <v>24.1</v>
+        <v>24.5</v>
       </c>
       <c r="AA3" t="n">
         <v>25.8</v>
       </c>
       <c r="AB3" t="n">
-        <v>94.7</v>
+        <v>94.3</v>
       </c>
       <c r="AC3" t="n">
         <v>4.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
       </c>
       <c r="AF3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH3" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AI3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AJ3" t="n">
         <v>28</v>
@@ -945,49 +1012,49 @@
         <v>17</v>
       </c>
       <c r="AL3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AM3" t="n">
         <v>15</v>
       </c>
       <c r="AN3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AO3" t="n">
         <v>2</v>
       </c>
       <c r="AP3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AQ3" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AR3" t="n">
         <v>19</v>
       </c>
       <c r="AS3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AT3" t="n">
         <v>10</v>
       </c>
       <c r="AU3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AV3" t="n">
         <v>30</v>
       </c>
       <c r="AW3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AX3" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AY3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BA3" t="n">
         <v>2</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>11-17-2008-09</t>
+          <t>2008-11-17</t>
         </is>
       </c>
     </row>
@@ -1103,13 +1170,13 @@
         <v>-4.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AE4" t="n">
         <v>24</v>
       </c>
       <c r="AF4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG4" t="n">
         <v>24</v>
@@ -1127,22 +1194,22 @@
         <v>22</v>
       </c>
       <c r="AL4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AM4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AN4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AP4" t="n">
         <v>10</v>
       </c>
       <c r="AQ4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR4" t="n">
         <v>11</v>
@@ -1154,13 +1221,13 @@
         <v>30</v>
       </c>
       <c r="AU4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AV4" t="n">
         <v>19</v>
       </c>
       <c r="AW4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AX4" t="n">
         <v>25</v>
@@ -1169,10 +1236,10 @@
         <v>30</v>
       </c>
       <c r="AZ4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BB4" t="n">
         <v>30</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>11-17-2008-09</t>
+          <t>2008-11-17</t>
         </is>
       </c>
     </row>
@@ -1207,16 +1274,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5" t="n">
         <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.444</v>
+        <v>0.5</v>
       </c>
       <c r="H5" t="n">
         <v>48</v>
@@ -1225,43 +1292,43 @@
         <v>35.1</v>
       </c>
       <c r="J5" t="n">
-        <v>85.2</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>0.412</v>
+        <v>0.42</v>
       </c>
       <c r="L5" t="n">
         <v>5.3</v>
       </c>
       <c r="M5" t="n">
-        <v>14.7</v>
+        <v>14.4</v>
       </c>
       <c r="N5" t="n">
-        <v>0.364</v>
+        <v>0.368</v>
       </c>
       <c r="O5" t="n">
-        <v>21</v>
+        <v>22.2</v>
       </c>
       <c r="P5" t="n">
-        <v>26.3</v>
+        <v>28.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.797</v>
+        <v>0.79</v>
       </c>
       <c r="R5" t="n">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
       <c r="S5" t="n">
-        <v>32.6</v>
+        <v>31.9</v>
       </c>
       <c r="T5" t="n">
-        <v>45.2</v>
+        <v>44.7</v>
       </c>
       <c r="U5" t="n">
-        <v>17.6</v>
+        <v>18.5</v>
       </c>
       <c r="V5" t="n">
-        <v>13.6</v>
+        <v>14.1</v>
       </c>
       <c r="W5" t="n">
         <v>8.699999999999999</v>
@@ -1270,98 +1337,98 @@
         <v>5.8</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
       <c r="Z5" t="n">
-        <v>22.6</v>
+        <v>22.1</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.4</v>
+        <v>22.3</v>
       </c>
       <c r="AB5" t="n">
-        <v>96.59999999999999</v>
+        <v>97.7</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD5" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="AE5" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AF5" t="n">
         <v>15</v>
       </c>
       <c r="AG5" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AH5" t="n">
         <v>17</v>
       </c>
       <c r="AI5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AJ5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL5" t="n">
         <v>18</v>
       </c>
       <c r="AM5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AN5" t="n">
         <v>12</v>
       </c>
       <c r="AO5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP5" t="n">
         <v>8</v>
       </c>
-      <c r="AP5" t="n">
-        <v>13</v>
-      </c>
       <c r="AQ5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AR5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AS5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT5" t="n">
         <v>7</v>
       </c>
-      <c r="AT5" t="n">
-        <v>6</v>
-      </c>
       <c r="AU5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY5" t="n">
         <v>25</v>
       </c>
-      <c r="AV5" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>28</v>
-      </c>
       <c r="AZ5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BA5" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>14</v>
+      </c>
+      <c r="BC5" t="n">
         <v>15</v>
       </c>
-      <c r="BB5" t="n">
-        <v>19</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>18</v>
-      </c>
       <c r="BD5" t="n">
         <v>10</v>
       </c>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>11-17-2008-09</t>
+          <t>2008-11-17</t>
         </is>
       </c>
     </row>
@@ -1389,157 +1456,157 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
         <v>8</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>0.889</v>
+        <v>0.8</v>
       </c>
       <c r="H6" t="n">
         <v>48</v>
       </c>
       <c r="I6" t="n">
-        <v>37.7</v>
+        <v>36.8</v>
       </c>
       <c r="J6" t="n">
-        <v>77.8</v>
+        <v>76.8</v>
       </c>
       <c r="K6" t="n">
-        <v>0.484</v>
+        <v>0.479</v>
       </c>
       <c r="L6" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="M6" t="n">
-        <v>19.3</v>
+        <v>18.9</v>
       </c>
       <c r="N6" t="n">
-        <v>0.339</v>
+        <v>0.328</v>
       </c>
       <c r="O6" t="n">
-        <v>21</v>
+        <v>21.3</v>
       </c>
       <c r="P6" t="n">
-        <v>26.6</v>
+        <v>27.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.791</v>
+        <v>0.783</v>
       </c>
       <c r="R6" t="n">
-        <v>10.9</v>
+        <v>10.6</v>
       </c>
       <c r="S6" t="n">
-        <v>28.7</v>
+        <v>29.1</v>
       </c>
       <c r="T6" t="n">
-        <v>39.6</v>
+        <v>39.7</v>
       </c>
       <c r="U6" t="n">
-        <v>21.2</v>
+        <v>20.7</v>
       </c>
       <c r="V6" t="n">
-        <v>12.9</v>
+        <v>13.8</v>
       </c>
       <c r="W6" t="n">
         <v>8</v>
       </c>
       <c r="X6" t="n">
-        <v>6.1</v>
+        <v>5.7</v>
       </c>
       <c r="Y6" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="Z6" t="n">
-        <v>21.4</v>
+        <v>21.9</v>
       </c>
       <c r="AA6" t="n">
-        <v>21.7</v>
+        <v>22.3</v>
       </c>
       <c r="AB6" t="n">
-        <v>102.9</v>
+        <v>101.1</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.9</v>
+        <v>7.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="AE6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AH6" t="n">
         <v>17</v>
       </c>
       <c r="AI6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AJ6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AM6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AN6" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AO6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AP6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AQ6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AR6" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AS6" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AT6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AW6" t="n">
         <v>9</v>
       </c>
       <c r="AX6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AY6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AZ6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BA6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BB6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BC6" t="n">
         <v>2</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>11-17-2008-09</t>
+          <t>2008-11-17</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>-2.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE7" t="n">
         <v>24</v>
@@ -1664,7 +1731,7 @@
         <v>8</v>
       </c>
       <c r="AI7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ7" t="n">
         <v>3</v>
@@ -1673,7 +1740,7 @@
         <v>24</v>
       </c>
       <c r="AL7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AM7" t="n">
         <v>11</v>
@@ -1682,28 +1749,28 @@
         <v>26</v>
       </c>
       <c r="AO7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AP7" t="n">
         <v>19</v>
       </c>
       <c r="AQ7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR7" t="n">
         <v>5</v>
       </c>
       <c r="AS7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT7" t="n">
         <v>3</v>
       </c>
       <c r="AU7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW7" t="n">
         <v>12</v>
@@ -1712,19 +1779,19 @@
         <v>18</v>
       </c>
       <c r="AY7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BA7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB7" t="n">
         <v>9</v>
       </c>
       <c r="BC7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>11-17-2008-09</t>
+          <t>2008-11-17</t>
         </is>
       </c>
     </row>
@@ -1831,16 +1898,16 @@
         <v>1.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF8" t="n">
         <v>8</v>
       </c>
       <c r="AG8" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AH8" t="n">
         <v>8</v>
@@ -1855,13 +1922,13 @@
         <v>20</v>
       </c>
       <c r="AL8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AM8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AN8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
@@ -1870,22 +1937,22 @@
         <v>2</v>
       </c>
       <c r="AQ8" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AR8" t="n">
         <v>25</v>
       </c>
       <c r="AS8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AT8" t="n">
         <v>11</v>
       </c>
       <c r="AU8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW8" t="n">
         <v>2</v>
@@ -1894,13 +1961,13 @@
         <v>14</v>
       </c>
       <c r="AY8" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AZ8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB8" t="n">
         <v>11</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>11-17-2008-09</t>
+          <t>2008-11-17</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>2.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE9" t="n">
         <v>4</v>
@@ -2022,7 +2089,7 @@
         <v>4</v>
       </c>
       <c r="AG9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH9" t="n">
         <v>17</v>
@@ -2034,28 +2101,28 @@
         <v>12</v>
       </c>
       <c r="AK9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AL9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AM9" t="n">
         <v>21</v>
       </c>
       <c r="AN9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AO9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AP9" t="n">
         <v>9</v>
       </c>
       <c r="AQ9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AR9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AS9" t="n">
         <v>17</v>
@@ -2064,31 +2131,31 @@
         <v>11</v>
       </c>
       <c r="AU9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>19</v>
+      </c>
+      <c r="AX9" t="n">
         <v>9</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>20</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>11</v>
       </c>
       <c r="AY9" t="n">
         <v>11</v>
       </c>
       <c r="AZ9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BB9" t="n">
         <v>8</v>
       </c>
       <c r="BC9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>11-17-2008-09</t>
+          <t>2008-11-17</t>
         </is>
       </c>
     </row>
@@ -2195,13 +2262,13 @@
         <v>-0.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE10" t="n">
         <v>19</v>
       </c>
       <c r="AF10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG10" t="n">
         <v>22</v>
@@ -2219,7 +2286,7 @@
         <v>21</v>
       </c>
       <c r="AL10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM10" t="n">
         <v>13</v>
@@ -2228,7 +2295,7 @@
         <v>28</v>
       </c>
       <c r="AO10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AP10" t="n">
         <v>1</v>
@@ -2237,13 +2304,13 @@
         <v>29</v>
       </c>
       <c r="AR10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AU10" t="n">
         <v>21</v>
@@ -2255,22 +2322,22 @@
         <v>15</v>
       </c>
       <c r="AX10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY10" t="n">
         <v>24</v>
       </c>
       <c r="AZ10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA10" t="n">
         <v>1</v>
       </c>
       <c r="BB10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BC10" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>11-17-2008-09</t>
+          <t>2008-11-17</t>
         </is>
       </c>
     </row>
@@ -2299,121 +2366,121 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F11" t="n">
         <v>4</v>
       </c>
       <c r="G11" t="n">
-        <v>0.636</v>
+        <v>0.6</v>
       </c>
       <c r="H11" t="n">
         <v>48.5</v>
       </c>
       <c r="I11" t="n">
-        <v>33.7</v>
+        <v>32.9</v>
       </c>
       <c r="J11" t="n">
-        <v>78.90000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="K11" t="n">
-        <v>0.427</v>
+        <v>0.419</v>
       </c>
       <c r="L11" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="M11" t="n">
-        <v>16.2</v>
+        <v>17</v>
       </c>
       <c r="N11" t="n">
-        <v>0.354</v>
+        <v>0.365</v>
       </c>
       <c r="O11" t="n">
-        <v>19.1</v>
+        <v>19.5</v>
       </c>
       <c r="P11" t="n">
-        <v>22.6</v>
+        <v>23.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.843</v>
+        <v>0.837</v>
       </c>
       <c r="R11" t="n">
-        <v>11</v>
+        <v>10.7</v>
       </c>
       <c r="S11" t="n">
-        <v>31.7</v>
+        <v>31.5</v>
       </c>
       <c r="T11" t="n">
-        <v>42.7</v>
+        <v>42.2</v>
       </c>
       <c r="U11" t="n">
-        <v>17.3</v>
+        <v>17.2</v>
       </c>
       <c r="V11" t="n">
-        <v>13.6</v>
+        <v>13.3</v>
       </c>
       <c r="W11" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="X11" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Y11" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Z11" t="n">
-        <v>17.7</v>
+        <v>17.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>92.3</v>
+        <v>91.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE11" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AF11" t="n">
         <v>8</v>
       </c>
       <c r="AG11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>29</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AM11" t="n">
         <v>14</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>28</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>20</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>17</v>
       </c>
       <c r="AN11" t="n">
         <v>13</v>
       </c>
       <c r="AO11" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AP11" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AQ11" t="n">
         <v>1</v>
@@ -2422,37 +2489,37 @@
         <v>20</v>
       </c>
       <c r="AS11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AT11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU11" t="n">
         <v>26</v>
       </c>
       <c r="AV11" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AW11" t="n">
         <v>17</v>
       </c>
       <c r="AX11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AY11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ11" t="n">
         <v>1</v>
       </c>
       <c r="BA11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BC11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>11-17-2008-09</t>
+          <t>2008-11-17</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>2</v>
       </c>
       <c r="AD12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AE12" t="n">
         <v>19</v>
@@ -2577,10 +2644,10 @@
         <v>10</v>
       </c>
       <c r="AJ12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AK12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL12" t="n">
         <v>9</v>
@@ -2589,16 +2656,16 @@
         <v>5</v>
       </c>
       <c r="AN12" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AO12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP12" t="n">
         <v>22</v>
       </c>
-      <c r="AP12" t="n">
-        <v>23</v>
-      </c>
       <c r="AQ12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AR12" t="n">
         <v>14</v>
@@ -2607,7 +2674,7 @@
         <v>4</v>
       </c>
       <c r="AT12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AU12" t="n">
         <v>5</v>
@@ -2625,7 +2692,7 @@
         <v>26</v>
       </c>
       <c r="AZ12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA12" t="n">
         <v>21</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>11-17-2008-09</t>
+          <t>2008-11-17</t>
         </is>
       </c>
     </row>
@@ -2663,154 +2730,154 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1</v>
+        <v>0.111</v>
       </c>
       <c r="H13" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I13" t="n">
-        <v>34</v>
+        <v>33.8</v>
       </c>
       <c r="J13" t="n">
-        <v>82.59999999999999</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>0.412</v>
+        <v>0.411</v>
       </c>
       <c r="L13" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="M13" t="n">
-        <v>18.2</v>
+        <v>18.4</v>
       </c>
       <c r="N13" t="n">
-        <v>0.308</v>
+        <v>0.319</v>
       </c>
       <c r="O13" t="n">
-        <v>15.6</v>
+        <v>16.4</v>
       </c>
       <c r="P13" t="n">
-        <v>21.4</v>
+        <v>22.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.729</v>
+        <v>0.725</v>
       </c>
       <c r="R13" t="n">
-        <v>11.6</v>
+        <v>11.3</v>
       </c>
       <c r="S13" t="n">
-        <v>28.9</v>
+        <v>28.4</v>
       </c>
       <c r="T13" t="n">
-        <v>40.5</v>
+        <v>39.8</v>
       </c>
       <c r="U13" t="n">
-        <v>19.4</v>
+        <v>19.1</v>
       </c>
       <c r="V13" t="n">
-        <v>15.4</v>
+        <v>15.7</v>
       </c>
       <c r="W13" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="X13" t="n">
-        <v>6.8</v>
+        <v>6.1</v>
       </c>
       <c r="Y13" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="Z13" t="n">
-        <v>22.6</v>
+        <v>24.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>19.7</v>
+        <v>20.2</v>
       </c>
       <c r="AB13" t="n">
-        <v>89.2</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="AC13" t="n">
-        <v>-12.8</v>
+        <v>-13.9</v>
       </c>
       <c r="AD13" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="AE13" t="n">
         <v>27</v>
       </c>
       <c r="AF13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AG13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AH13" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AI13" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AJ13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AK13" t="n">
         <v>29</v>
       </c>
       <c r="AL13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AM13" t="n">
         <v>12</v>
       </c>
       <c r="AN13" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AO13" t="n">
         <v>29</v>
       </c>
       <c r="AP13" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AQ13" t="n">
         <v>27</v>
       </c>
       <c r="AR13" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AS13" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AT13" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AU13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AV13" t="n">
         <v>20</v>
       </c>
       <c r="AW13" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AX13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AY13" t="n">
         <v>13</v>
       </c>
       <c r="AZ13" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="BA13" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BB13" t="n">
         <v>29</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>11-17-2008-09</t>
+          <t>2008-11-17</t>
         </is>
       </c>
     </row>
@@ -2845,136 +2912,136 @@
         </is>
       </c>
       <c r="D14" t="n">
+        <v>8</v>
+      </c>
+      <c r="E14" t="n">
         <v>7</v>
-      </c>
-      <c r="E14" t="n">
-        <v>6</v>
       </c>
       <c r="F14" t="n">
         <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>0.857</v>
+        <v>0.875</v>
       </c>
       <c r="H14" t="n">
         <v>48</v>
       </c>
       <c r="I14" t="n">
-        <v>37.6</v>
+        <v>37.5</v>
       </c>
       <c r="J14" t="n">
-        <v>85.59999999999999</v>
+        <v>84.8</v>
       </c>
       <c r="K14" t="n">
-        <v>0.439</v>
+        <v>0.442</v>
       </c>
       <c r="L14" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="M14" t="n">
-        <v>17.6</v>
+        <v>16.6</v>
       </c>
       <c r="N14" t="n">
-        <v>0.366</v>
+        <v>0.391</v>
       </c>
       <c r="O14" t="n">
+        <v>22</v>
+      </c>
+      <c r="P14" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.759</v>
+      </c>
+      <c r="R14" t="n">
+        <v>14</v>
+      </c>
+      <c r="S14" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="T14" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="U14" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="V14" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="W14" t="n">
+        <v>10</v>
+      </c>
+      <c r="X14" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="AA14" t="n">
         <v>23</v>
       </c>
-      <c r="P14" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0.752</v>
-      </c>
-      <c r="R14" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="S14" t="n">
-        <v>33.7</v>
-      </c>
-      <c r="T14" t="n">
-        <v>48.4</v>
-      </c>
-      <c r="U14" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="V14" t="n">
-        <v>14</v>
-      </c>
-      <c r="W14" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="X14" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>23.9</v>
-      </c>
       <c r="AB14" t="n">
-        <v>104.6</v>
+        <v>103.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>13.6</v>
+        <v>14.4</v>
       </c>
       <c r="AD14" t="n">
         <v>29</v>
       </c>
       <c r="AE14" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AF14" t="n">
         <v>1</v>
       </c>
       <c r="AG14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH14" t="n">
         <v>17</v>
       </c>
       <c r="AI14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>7</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>14</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>16</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP14" t="n">
         <v>6</v>
       </c>
-      <c r="AJ14" t="n">
-        <v>6</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>16</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>11</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>14</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>11</v>
-      </c>
-      <c r="AO14" t="n">
+      <c r="AQ14" t="n">
+        <v>18</v>
+      </c>
+      <c r="AR14" t="n">
         <v>3</v>
       </c>
-      <c r="AP14" t="n">
-        <v>3</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>19</v>
-      </c>
-      <c r="AR14" t="n">
+      <c r="AS14" t="n">
         <v>1</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>3</v>
       </c>
       <c r="AT14" t="n">
         <v>2</v>
       </c>
       <c r="AU14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AV14" t="n">
         <v>13</v>
@@ -2983,19 +3050,19 @@
         <v>1</v>
       </c>
       <c r="AX14" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AY14" t="n">
         <v>12</v>
       </c>
       <c r="AZ14" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BB14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BC14" t="n">
         <v>1</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>11-17-2008-09</t>
+          <t>2008-11-17</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-5.7</v>
       </c>
       <c r="AD15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE15" t="n">
         <v>24</v>
@@ -3138,40 +3205,40 @@
         <v>27</v>
       </c>
       <c r="AO15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AP15" t="n">
         <v>14</v>
       </c>
       <c r="AQ15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR15" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AS15" t="n">
         <v>12</v>
       </c>
       <c r="AT15" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AU15" t="n">
         <v>30</v>
       </c>
       <c r="AV15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX15" t="n">
         <v>18</v>
       </c>
       <c r="AY15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ15" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BA15" t="n">
         <v>16</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>11-17-2008-09</t>
+          <t>2008-11-17</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>4.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE16" t="n">
         <v>13</v>
@@ -3308,7 +3375,7 @@
         <v>15</v>
       </c>
       <c r="AK16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL16" t="n">
         <v>8</v>
@@ -3326,7 +3393,7 @@
         <v>16</v>
       </c>
       <c r="AQ16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR16" t="n">
         <v>17</v>
@@ -3335,13 +3402,13 @@
         <v>27</v>
       </c>
       <c r="AT16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AU16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AV16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW16" t="n">
         <v>3</v>
@@ -3350,10 +3417,10 @@
         <v>13</v>
       </c>
       <c r="AY16" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AZ16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA16" t="n">
         <v>20</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>11-17-2008-09</t>
+          <t>2008-11-17</t>
         </is>
       </c>
     </row>
@@ -3391,109 +3458,109 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E17" t="n">
         <v>5</v>
       </c>
       <c r="F17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5</v>
+        <v>0.455</v>
       </c>
       <c r="H17" t="n">
-        <v>49.5</v>
+        <v>49.4</v>
       </c>
       <c r="I17" t="n">
-        <v>34.7</v>
+        <v>34.9</v>
       </c>
       <c r="J17" t="n">
-        <v>82.3</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>0.422</v>
+        <v>0.426</v>
       </c>
       <c r="L17" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="M17" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="N17" t="n">
-        <v>0.351</v>
+        <v>0.358</v>
       </c>
       <c r="O17" t="n">
-        <v>20.8</v>
+        <v>20.3</v>
       </c>
       <c r="P17" t="n">
-        <v>27.7</v>
+        <v>27</v>
       </c>
       <c r="Q17" t="n">
         <v>0.751</v>
       </c>
       <c r="R17" t="n">
-        <v>14</v>
+        <v>13.9</v>
       </c>
       <c r="S17" t="n">
-        <v>31.5</v>
+        <v>30.4</v>
       </c>
       <c r="T17" t="n">
-        <v>45.5</v>
+        <v>44.3</v>
       </c>
       <c r="U17" t="n">
         <v>20.5</v>
       </c>
       <c r="V17" t="n">
-        <v>16</v>
+        <v>16.3</v>
       </c>
       <c r="W17" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="X17" t="n">
         <v>3.3</v>
       </c>
       <c r="Y17" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Z17" t="n">
-        <v>24.8</v>
+        <v>25.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>25.3</v>
+        <v>24.6</v>
       </c>
       <c r="AB17" t="n">
         <v>94.90000000000001</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.1</v>
+        <v>-1.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AE17" t="n">
         <v>13</v>
       </c>
       <c r="AF17" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AG17" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AH17" t="n">
         <v>2</v>
       </c>
       <c r="AI17" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AJ17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AK17" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL17" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AM17" t="n">
         <v>27</v>
@@ -3502,10 +3569,10 @@
         <v>14</v>
       </c>
       <c r="AO17" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AP17" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AQ17" t="n">
         <v>21</v>
@@ -3514,37 +3581,37 @@
         <v>4</v>
       </c>
       <c r="AS17" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AT17" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AU17" t="n">
         <v>11</v>
       </c>
       <c r="AV17" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AW17" t="n">
         <v>26</v>
       </c>
       <c r="AX17" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AY17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BA17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC17" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>11-17-2008-09</t>
+          <t>2008-11-17</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-5</v>
       </c>
       <c r="AD18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AE18" t="n">
         <v>27</v>
@@ -3666,7 +3733,7 @@
         <v>1</v>
       </c>
       <c r="AI18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ18" t="n">
         <v>4</v>
@@ -3684,10 +3751,10 @@
         <v>29</v>
       </c>
       <c r="AO18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ18" t="n">
         <v>3</v>
@@ -3711,13 +3778,13 @@
         <v>28</v>
       </c>
       <c r="AX18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY18" t="n">
         <v>23</v>
       </c>
       <c r="AZ18" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BA18" t="n">
         <v>22</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>11-17-2008-09</t>
+          <t>2008-11-17</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>-3.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AE19" t="n">
         <v>19</v>
@@ -3866,19 +3933,19 @@
         <v>4</v>
       </c>
       <c r="AO19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AP19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AR19" t="n">
         <v>15</v>
       </c>
       <c r="AS19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT19" t="n">
         <v>19</v>
@@ -3890,7 +3957,7 @@
         <v>15</v>
       </c>
       <c r="AW19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX19" t="n">
         <v>15</v>
@@ -3899,7 +3966,7 @@
         <v>17</v>
       </c>
       <c r="AZ19" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BA19" t="n">
         <v>17</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>11-17-2008-09</t>
+          <t>2008-11-17</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>2.1</v>
       </c>
       <c r="AD20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AE20" t="n">
         <v>13</v>
@@ -4030,31 +4097,31 @@
         <v>30</v>
       </c>
       <c r="AI20" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ20" t="n">
         <v>26</v>
       </c>
       <c r="AK20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AM20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AN20" t="n">
         <v>6</v>
       </c>
       <c r="AO20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP20" t="n">
         <v>20</v>
       </c>
       <c r="AQ20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR20" t="n">
         <v>26</v>
@@ -4063,13 +4130,13 @@
         <v>25</v>
       </c>
       <c r="AT20" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AU20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AV20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW20" t="n">
         <v>9</v>
@@ -4078,13 +4145,13 @@
         <v>26</v>
       </c>
       <c r="AY20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AZ20" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BA20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BB20" t="n">
         <v>24</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>11-17-2008-09</t>
+          <t>2008-11-17</t>
         </is>
       </c>
     </row>
@@ -4197,16 +4264,16 @@
         <v>0.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF21" t="n">
         <v>8</v>
       </c>
       <c r="AG21" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AH21" t="n">
         <v>8</v>
@@ -4218,7 +4285,7 @@
         <v>2</v>
       </c>
       <c r="AK21" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL21" t="n">
         <v>1</v>
@@ -4227,46 +4294,46 @@
         <v>1</v>
       </c>
       <c r="AN21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO21" t="n">
         <v>28</v>
       </c>
       <c r="AP21" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ21" t="n">
         <v>22</v>
       </c>
       <c r="AR21" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AS21" t="n">
         <v>11</v>
       </c>
       <c r="AT21" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AU21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV21" t="n">
         <v>17</v>
       </c>
       <c r="AW21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
       </c>
       <c r="AY21" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AZ21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA21" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BB21" t="n">
         <v>1</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>11-17-2008-09</t>
+          <t>2008-11-17</t>
         </is>
       </c>
     </row>
@@ -4301,28 +4368,28 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G22" t="n">
-        <v>0.091</v>
+        <v>0.1</v>
       </c>
       <c r="H22" t="n">
         <v>48</v>
       </c>
       <c r="I22" t="n">
-        <v>35</v>
+        <v>35.1</v>
       </c>
       <c r="J22" t="n">
-        <v>85.90000000000001</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>0.407</v>
+        <v>0.408</v>
       </c>
       <c r="L22" t="n">
         <v>2.6</v>
@@ -4331,55 +4398,55 @@
         <v>7.8</v>
       </c>
       <c r="N22" t="n">
-        <v>0.337</v>
+        <v>0.333</v>
       </c>
       <c r="O22" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="P22" t="n">
-        <v>23.4</v>
+        <v>23</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.735</v>
+        <v>0.743</v>
       </c>
       <c r="R22" t="n">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="S22" t="n">
-        <v>31.8</v>
+        <v>32.5</v>
       </c>
       <c r="T22" t="n">
-        <v>44.6</v>
+        <v>45.2</v>
       </c>
       <c r="U22" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="V22" t="n">
-        <v>15.8</v>
+        <v>16.1</v>
       </c>
       <c r="W22" t="n">
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
       <c r="X22" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Y22" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="Z22" t="n">
-        <v>22.4</v>
+        <v>22.8</v>
       </c>
       <c r="AA22" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="AB22" t="n">
-        <v>89.8</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="AC22" t="n">
-        <v>-10.5</v>
+        <v>-10.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE22" t="n">
         <v>27</v>
@@ -4394,7 +4461,7 @@
         <v>17</v>
       </c>
       <c r="AI22" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AJ22" t="n">
         <v>5</v>
@@ -4409,43 +4476,43 @@
         <v>30</v>
       </c>
       <c r="AN22" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO22" t="n">
         <v>27</v>
       </c>
       <c r="AP22" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AR22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS22" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AT22" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AU22" t="n">
         <v>27</v>
       </c>
       <c r="AV22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW22" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AX22" t="n">
         <v>21</v>
       </c>
       <c r="AY22" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AZ22" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="BA22" t="n">
         <v>28</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>11-17-2008-09</t>
+          <t>2008-11-17</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>5.7</v>
       </c>
       <c r="AD23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE23" t="n">
         <v>4</v>
@@ -4570,13 +4637,13 @@
         <v>4</v>
       </c>
       <c r="AG23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH23" t="n">
         <v>17</v>
       </c>
       <c r="AI23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ23" t="n">
         <v>15</v>
@@ -4585,7 +4652,7 @@
         <v>15</v>
       </c>
       <c r="AL23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM23" t="n">
         <v>2</v>
@@ -4597,7 +4664,7 @@
         <v>11</v>
       </c>
       <c r="AP23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AQ23" t="n">
         <v>30</v>
@@ -4606,16 +4673,16 @@
         <v>10</v>
       </c>
       <c r="AS23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AU23" t="n">
         <v>29</v>
       </c>
       <c r="AV23" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AW23" t="n">
         <v>15</v>
@@ -4624,13 +4691,13 @@
         <v>1</v>
       </c>
       <c r="AY23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AZ23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BB23" t="n">
         <v>7</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>11-17-2008-09</t>
+          <t>2008-11-17</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>3.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE24" t="n">
         <v>13</v>
@@ -4758,13 +4825,13 @@
         <v>17</v>
       </c>
       <c r="AI24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AJ24" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AK24" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AL24" t="n">
         <v>22</v>
@@ -4773,19 +4840,19 @@
         <v>28</v>
       </c>
       <c r="AN24" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AO24" t="n">
         <v>26</v>
       </c>
       <c r="AP24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AQ24" t="n">
         <v>20</v>
       </c>
       <c r="AR24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS24" t="n">
         <v>1</v>
@@ -4794,19 +4861,19 @@
         <v>1</v>
       </c>
       <c r="AU24" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AV24" t="n">
         <v>26</v>
       </c>
       <c r="AW24" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AX24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ24" t="n">
         <v>2</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>11-17-2008-09</t>
+          <t>2008-11-17</t>
         </is>
       </c>
     </row>
@@ -4847,97 +4914,97 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E25" t="n">
         <v>8</v>
       </c>
       <c r="F25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G25" t="n">
-        <v>0.667</v>
+        <v>0.727</v>
       </c>
       <c r="H25" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I25" t="n">
-        <v>36.4</v>
+        <v>36.5</v>
       </c>
       <c r="J25" t="n">
-        <v>73</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>0.499</v>
+        <v>0.5</v>
       </c>
       <c r="L25" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="M25" t="n">
         <v>16</v>
       </c>
       <c r="N25" t="n">
-        <v>0.38</v>
+        <v>0.386</v>
       </c>
       <c r="O25" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="P25" t="n">
-        <v>28.9</v>
+        <v>29.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.746</v>
+        <v>0.747</v>
       </c>
       <c r="R25" t="n">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="S25" t="n">
-        <v>31.3</v>
+        <v>32.3</v>
       </c>
       <c r="T25" t="n">
-        <v>39.3</v>
+        <v>40.5</v>
       </c>
       <c r="U25" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="V25" t="n">
-        <v>16.8</v>
+        <v>17.1</v>
       </c>
       <c r="W25" t="n">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="X25" t="n">
         <v>5.1</v>
       </c>
       <c r="Y25" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>20.8</v>
+        <v>20.1</v>
       </c>
       <c r="AA25" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="AB25" t="n">
-        <v>100.5</v>
+        <v>100.8</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
       <c r="AD25" t="n">
         <v>1</v>
       </c>
       <c r="AE25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF25" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AG25" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AH25" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AI25" t="n">
         <v>11</v>
@@ -4949,7 +5016,7 @@
         <v>1</v>
       </c>
       <c r="AL25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AM25" t="n">
         <v>19</v>
@@ -4961,7 +5028,7 @@
         <v>6</v>
       </c>
       <c r="AP25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AQ25" t="n">
         <v>23</v>
@@ -4970,37 +5037,37 @@
         <v>29</v>
       </c>
       <c r="AS25" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>18</v>
+      </c>
+      <c r="AU25" t="n">
         <v>14</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>23</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>15</v>
       </c>
       <c r="AV25" t="n">
         <v>29</v>
       </c>
       <c r="AW25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AX25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY25" t="n">
         <v>10</v>
       </c>
       <c r="AZ25" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BA25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BB25" t="n">
         <v>6</v>
       </c>
       <c r="BC25" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>11-17-2008-09</t>
+          <t>2008-11-17</t>
         </is>
       </c>
     </row>
@@ -5029,127 +5096,127 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E26" t="n">
         <v>6</v>
       </c>
       <c r="F26" t="n">
+        <v>4</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H26" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="I26" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="J26" t="n">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.441</v>
+      </c>
+      <c r="L26" t="n">
+        <v>8</v>
+      </c>
+      <c r="M26" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.404</v>
+      </c>
+      <c r="O26" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="P26" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.773</v>
+      </c>
+      <c r="R26" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="S26" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="T26" t="n">
+        <v>39</v>
+      </c>
+      <c r="U26" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="V26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="W26" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="X26" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>22</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>16</v>
+      </c>
+      <c r="AL26" t="n">
         <v>3</v>
       </c>
-      <c r="G26" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="H26" t="n">
-        <v>48.6</v>
-      </c>
-      <c r="I26" t="n">
-        <v>35.2</v>
-      </c>
-      <c r="J26" t="n">
-        <v>77.8</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0.453</v>
-      </c>
-      <c r="L26" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="M26" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0.402</v>
-      </c>
-      <c r="O26" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="P26" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0.787</v>
-      </c>
-      <c r="R26" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="S26" t="n">
-        <v>27</v>
-      </c>
-      <c r="T26" t="n">
-        <v>38.4</v>
-      </c>
-      <c r="U26" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="V26" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="W26" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="X26" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>96.7</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>19</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>8</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG26" t="n">
+      <c r="AM26" t="n">
         <v>6</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>6</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>16</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>8</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>4</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>8</v>
       </c>
       <c r="AN26" t="n">
         <v>2</v>
       </c>
       <c r="AO26" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AP26" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="AQ26" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AR26" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AS26" t="n">
         <v>29</v>
@@ -5164,25 +5231,25 @@
         <v>1</v>
       </c>
       <c r="AW26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AX26" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AY26" t="n">
         <v>1</v>
       </c>
       <c r="AZ26" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA26" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BB26" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BC26" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>11-17-2008-09</t>
+          <t>2008-11-17</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-4.8</v>
       </c>
       <c r="AD27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE27" t="n">
         <v>19</v>
@@ -5307,10 +5374,10 @@
         <v>3</v>
       </c>
       <c r="AJ27" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AK27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL27" t="n">
         <v>23</v>
@@ -5319,16 +5386,16 @@
         <v>22</v>
       </c>
       <c r="AN27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AR27" t="n">
         <v>27</v>
@@ -5337,25 +5404,25 @@
         <v>18</v>
       </c>
       <c r="AT27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU27" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AV27" t="n">
         <v>27</v>
       </c>
       <c r="AW27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AX27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY27" t="n">
         <v>18</v>
       </c>
       <c r="AZ27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA27" t="n">
         <v>19</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>11-17-2008-09</t>
+          <t>2008-11-17</t>
         </is>
       </c>
     </row>
@@ -5393,94 +5460,94 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F28" t="n">
         <v>5</v>
       </c>
       <c r="G28" t="n">
-        <v>0.5</v>
+        <v>0.444</v>
       </c>
       <c r="H28" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
       <c r="I28" t="n">
         <v>35.8</v>
       </c>
       <c r="J28" t="n">
-        <v>77.90000000000001</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>0.46</v>
+        <v>0.461</v>
       </c>
       <c r="L28" t="n">
         <v>7.7</v>
       </c>
       <c r="M28" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="N28" t="n">
         <v>0.397</v>
       </c>
       <c r="O28" t="n">
-        <v>12</v>
+        <v>12.7</v>
       </c>
       <c r="P28" t="n">
-        <v>16.1</v>
+        <v>17.2</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.745</v>
+        <v>0.735</v>
       </c>
       <c r="R28" t="n">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="S28" t="n">
         <v>31.2</v>
       </c>
       <c r="T28" t="n">
-        <v>38.9</v>
+        <v>39.2</v>
       </c>
       <c r="U28" t="n">
-        <v>20.2</v>
+        <v>19.7</v>
       </c>
       <c r="V28" t="n">
-        <v>12.3</v>
+        <v>11.9</v>
       </c>
       <c r="W28" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="X28" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="Z28" t="n">
-        <v>18.6</v>
+        <v>19</v>
       </c>
       <c r="AA28" t="n">
-        <v>17.4</v>
+        <v>18.3</v>
       </c>
       <c r="AB28" t="n">
-        <v>91.3</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="AC28" t="n">
-        <v>-2</v>
+        <v>-2.6</v>
       </c>
       <c r="AD28" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="AE28" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="AF28" t="n">
         <v>15</v>
       </c>
       <c r="AG28" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AH28" t="n">
         <v>3</v>
@@ -5489,7 +5556,7 @@
         <v>14</v>
       </c>
       <c r="AJ28" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AK28" t="n">
         <v>5</v>
@@ -5498,7 +5565,7 @@
         <v>6</v>
       </c>
       <c r="AM28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AN28" t="n">
         <v>5</v>
@@ -5510,19 +5577,19 @@
         <v>30</v>
       </c>
       <c r="AQ28" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AR28" t="n">
         <v>30</v>
       </c>
       <c r="AS28" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AT28" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AU28" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AV28" t="n">
         <v>2</v>
@@ -5531,22 +5598,22 @@
         <v>30</v>
       </c>
       <c r="AX28" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AY28" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AZ28" t="n">
         <v>4</v>
       </c>
       <c r="BA28" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BB28" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BC28" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>11-17-2008-09</t>
+          <t>2008-11-17</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>-0.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AE29" t="n">
         <v>13</v>
@@ -5677,7 +5744,7 @@
         <v>6</v>
       </c>
       <c r="AL29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AM29" t="n">
         <v>20</v>
@@ -5701,10 +5768,10 @@
         <v>19</v>
       </c>
       <c r="AT29" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AU29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV29" t="n">
         <v>14</v>
@@ -5713,22 +5780,22 @@
         <v>28</v>
       </c>
       <c r="AX29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ29" t="n">
         <v>3</v>
       </c>
       <c r="BA29" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BB29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BC29" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>11-17-2008-09</t>
+          <t>2008-11-17</t>
         </is>
       </c>
     </row>
@@ -5757,94 +5824,94 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F30" t="n">
         <v>4</v>
       </c>
       <c r="G30" t="n">
-        <v>0.636</v>
+        <v>0.6</v>
       </c>
       <c r="H30" t="n">
         <v>48</v>
       </c>
       <c r="I30" t="n">
-        <v>37</v>
+        <v>36.7</v>
       </c>
       <c r="J30" t="n">
-        <v>79.2</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K30" t="n">
         <v>0.467</v>
       </c>
       <c r="L30" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="M30" t="n">
-        <v>12.2</v>
+        <v>12.6</v>
       </c>
       <c r="N30" t="n">
-        <v>0.343</v>
+        <v>0.341</v>
       </c>
       <c r="O30" t="n">
-        <v>19.3</v>
+        <v>18.6</v>
       </c>
       <c r="P30" t="n">
-        <v>25.3</v>
+        <v>24.2</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.763</v>
+        <v>0.769</v>
       </c>
       <c r="R30" t="n">
-        <v>13</v>
+        <v>12.6</v>
       </c>
       <c r="S30" t="n">
-        <v>29.5</v>
+        <v>29.4</v>
       </c>
       <c r="T30" t="n">
-        <v>42.5</v>
+        <v>42</v>
       </c>
       <c r="U30" t="n">
-        <v>24.3</v>
+        <v>23.9</v>
       </c>
       <c r="V30" t="n">
-        <v>15.6</v>
+        <v>16.1</v>
       </c>
       <c r="W30" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="X30" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Y30" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="Z30" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="AA30" t="n">
-        <v>22.8</v>
+        <v>22.3</v>
       </c>
       <c r="AB30" t="n">
-        <v>97.5</v>
+        <v>96.3</v>
       </c>
       <c r="AC30" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="AD30" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE30" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AF30" t="n">
         <v>8</v>
       </c>
       <c r="AG30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH30" t="n">
         <v>17</v>
@@ -5853,7 +5920,7 @@
         <v>9</v>
       </c>
       <c r="AJ30" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AK30" t="n">
         <v>4</v>
@@ -5868,49 +5935,49 @@
         <v>16</v>
       </c>
       <c r="AO30" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AP30" t="n">
         <v>17</v>
       </c>
       <c r="AQ30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR30" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AS30" t="n">
         <v>20</v>
       </c>
       <c r="AT30" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AU30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV30" t="n">
         <v>21</v>
       </c>
       <c r="AW30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AY30" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AZ30" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="BA30" t="n">
         <v>10</v>
       </c>
       <c r="BB30" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="BC30" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>11-17-2008-09</t>
+          <t>2008-11-17</t>
         </is>
       </c>
     </row>
@@ -6017,13 +6084,13 @@
         <v>-9.9</v>
       </c>
       <c r="AD31" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE31" t="n">
         <v>27</v>
       </c>
       <c r="AF31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG31" t="n">
         <v>27</v>
@@ -6035,7 +6102,7 @@
         <v>23</v>
       </c>
       <c r="AJ31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AK31" t="n">
         <v>19</v>
@@ -6050,7 +6117,7 @@
         <v>30</v>
       </c>
       <c r="AO31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AP31" t="n">
         <v>7</v>
@@ -6068,7 +6135,7 @@
         <v>29</v>
       </c>
       <c r="AU31" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AV31" t="n">
         <v>16</v>
@@ -6080,13 +6147,13 @@
         <v>20</v>
       </c>
       <c r="AY31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ31" t="n">
         <v>5</v>
       </c>
       <c r="BA31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BB31" t="n">
         <v>23</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>11-17-2008-09</t>
+          <t>2008-11-17</t>
         </is>
       </c>
     </row>
